--- a/data/output/2025/evaluasi_34.xlsx
+++ b/data/output/2025/evaluasi_34.xlsx
@@ -1624,7 +1624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,6 +1880,146 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.649581840922431</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>47.71373368804379</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.052272785402003</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.698823930811515</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1894,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,6 +2122,202 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.656021194152354</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.844594841640755</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>47.33009212345712</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.94398402033093</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>21.31368547886568</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3404</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sleman</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.116561194229031</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2084,6 +2420,230 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3737760645384534</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.719242740039451</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>42.94729791221372</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.402243898497733</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.267422601249805</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25.19920668543726</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3401</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kulon Progo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>18.67410195664591</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2200,18 +2760,186 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>1.17576520927853</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>68.96507298836752</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.75307655992452</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18.82747220619616</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.8979537220392</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3402</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bantul</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>-2.434185703140282</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2228,7 +2956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2291,6 +3019,146 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.1923461550780373</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.75017984989538</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>52.71818545146571</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3403</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2471224627036659</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
